--- a/jumia/jumia_nike_shoes.xlsx
+++ b/jumia/jumia_nike_shoes.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G71"/>
   <cols>
     <col min="1" max="1" width="40.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -1253,687 +1253,587 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>TIMBUTUS 5-layer Steel Pipe Shoe Rack (56 * 25.5 * 90cm)</v>
+        <v>TIMBUTUS 6-Tier Steel Pipe Shoe Rack</v>
       </c>
       <c r="B43" t="str">
-        <v>KSh 1,581</v>
+        <v>KSh 1,273</v>
       </c>
       <c r="C43" t="str">
-        <v>KSh 3,350</v>
+        <v>KSh 2,010</v>
       </c>
       <c r="D43" t="str">
-        <v>53%</v>
+        <v>37%</v>
       </c>
       <c r="F43" t="str">
-        <v>https://www.jumia.co.ke/timbutus-5-layer-steel-pipe-shoe-rack-56-25.5-90cm-303189222.html</v>
+        <v>https://www.jumia.co.ke/timbutus-6-tier-steel-pipe-shoe-rack-315586547.html</v>
       </c>
       <c r="G43" t="str">
-        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/22/2981303/1.jpg?6553</v>
+        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/74/5685513/1.jpg?8243</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Yxahee Shoe Rack Stackable Assembly Shoe Clothes Organizer-6 Layers</v>
+        <v>Lindy 8 Tier Shoe Rack - Silver/Black</v>
       </c>
       <c r="B44" t="str">
-        <v>KSh 1,453</v>
+        <v>KSh 995</v>
       </c>
       <c r="C44" t="str">
-        <v>KSh 2,005</v>
+        <v>KSh 1,350</v>
       </c>
       <c r="D44" t="str">
-        <v>28%</v>
+        <v>26%</v>
       </c>
       <c r="F44" t="str">
-        <v>https://www.jumia.co.ke/yxahee-shoe-rack-stackable-assembly-shoe-clothes-organizer-6-layers-274321014.html?seller_product=1</v>
+        <v>https://www.jumia.co.ke/lindy-8-tier-shoe-rack-silverblack-326119429.html</v>
       </c>
       <c r="G44" t="str">
-        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/41/0123472/1.jpg?6626</v>
+        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/92/4911623/1.jpg?3347</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Yxahee  3PCS PP Plastic Clear Shoe Boxes - Foldable Storage Organizer, Stackable for Dorm/Home, Space-Saving Shoe Cabinet Case</v>
+        <v>TIMBUTUS 5-layer Steel Pipe Shoe Rack (56 * 25.5 * 90cm)</v>
       </c>
       <c r="B45" t="str">
-        <v>KSh 1,474</v>
+        <v>KSh 1,581</v>
       </c>
       <c r="C45" t="str">
-        <v>KSh 2,680</v>
+        <v>KSh 3,350</v>
       </c>
       <c r="D45" t="str">
-        <v>45%</v>
+        <v>53%</v>
       </c>
       <c r="F45" t="str">
-        <v>https://www.jumia.co.ke/yxahee-3pcs-pp-plastic-clear-shoe-boxes-foldable-storage-organizer-stackable-for-dormhome-space-saving-shoe-cabinet-case-327528747.html</v>
+        <v>https://www.jumia.co.ke/timbutus-5-layer-steel-pipe-shoe-rack-56-25.5-90cm-303189222.html</v>
       </c>
       <c r="G45" t="str">
-        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/74/7825723/1.jpg?6209</v>
+        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/22/2981303/1.jpg?6553</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Yxahee Classy 3 Column Mobile Steel Wardrobe Closet(Red)</v>
+        <v>LM 6-Tier Shoe Organizer with Translucent Panels, Space-Saving Shoe Storage Cabinet for Entrance &amp; Home, 28×58×117cm</v>
       </c>
       <c r="B46" t="str">
-        <v>KSh 2,412</v>
+        <v>KSh 1,399</v>
       </c>
       <c r="C46" t="str">
-        <v>KSh 4,509</v>
+        <v>KSh 2,010</v>
       </c>
       <c r="D46" t="str">
-        <v>47%</v>
+        <v>30%</v>
       </c>
       <c r="F46" t="str">
-        <v>https://www.jumia.co.ke/yxahee-classy-3-column-mobile-steel-wardrobe-closetred-297108683.html?seller_product=1</v>
+        <v>https://www.jumia.co.ke/lm-6-tier-shoe-organizer-with-translucent-panels-space-saving-shoe-storage-cabinet-for-entrance-home-2858117cm-327990966.html</v>
       </c>
       <c r="G46" t="str">
-        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/38/6801792/1.jpg?2382</v>
+        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/66/9099723/1.jpg?6182</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>TIMBUTUS 6-Tier Steel Pipe Shoe Rack</v>
+        <v>Lindy Foldable Closet Cabinet - 10 Shelves - Grey</v>
       </c>
       <c r="B47" t="str">
-        <v>KSh 1,273</v>
+        <v>KSh 2,010</v>
       </c>
       <c r="C47" t="str">
-        <v>KSh 2,010</v>
+        <v>KSh 2,680</v>
       </c>
       <c r="D47" t="str">
-        <v>37%</v>
+        <v>25%</v>
       </c>
       <c r="F47" t="str">
-        <v>https://www.jumia.co.ke/timbutus-6-tier-steel-pipe-shoe-rack-315586547.html</v>
+        <v>https://www.jumia.co.ke/foldable-closet-cabinet-10-shelves-grey-lindy-mpg9519558.html</v>
       </c>
       <c r="G47" t="str">
-        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/74/5685513/1.jpg?8243</v>
+        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/30/0182523/1.jpg?5010</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Lindy 8 Tier Shoe Rack - Silver/Black</v>
+        <v>LM Mobile Garment Rack with Hanging Rail &amp; Storage Shelves, Space-Saving Clothes Organizer with Wheels, Black</v>
       </c>
       <c r="B48" t="str">
-        <v>KSh 995</v>
+        <v>KSh 1,420</v>
       </c>
       <c r="C48" t="str">
-        <v>KSh 1,350</v>
+        <v>KSh 1,742</v>
       </c>
       <c r="D48" t="str">
-        <v>26%</v>
+        <v>19%</v>
       </c>
       <c r="F48" t="str">
-        <v>https://www.jumia.co.ke/lindy-8-tier-shoe-rack-silverblack-326119429.html</v>
+        <v>https://www.jumia.co.ke/lm-mobile-garment-rack-with-hanging-rail-storage-shelves-space-saving-clothes-organizer-with-wheels-black-327991017.html</v>
       </c>
       <c r="G48" t="str">
-        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/92/4911623/1.jpg?3347</v>
+        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/71/0199723/1.jpg?7619</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Yxahee 5-Tier  Multifunctional Freestanding Shoe Rack Collapsible Shoe Rack</v>
+        <v>Shoe Rack Organizer for Entryway Space-Saving Design for Efficient Shoe Storage and Easy to Clean for Closets and Living Spaces</v>
       </c>
       <c r="B49" t="str">
-        <v>KSh 1,005</v>
+        <v>KSh 1,399</v>
       </c>
       <c r="C49" t="str">
-        <v>KSh 2,010</v>
+        <v>KSh 3,288</v>
       </c>
       <c r="D49" t="str">
-        <v>50%</v>
+        <v>58%</v>
       </c>
       <c r="F49" t="str">
-        <v>https://www.jumia.co.ke/yxahee-5-tier-multifunctional-freestanding-shoe-rack-collapsible-shoe-rack-327616106.html</v>
+        <v>https://www.jumia.co.ke/generic-shoe-rack-organizer-for-entryway-space-saving-design-for-efficient-shoe-storage-and-easy-to-clean-for-closets-and-living-spaces-326496878.html</v>
       </c>
       <c r="G49" t="str">
-        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/60/1616723/1.jpg?6310</v>
+        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/87/8694623/1.jpg?9672</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>LM 6-Tier Shoe Organizer with Translucent Panels, Space-Saving Shoe Storage Cabinet for Entrance &amp; Home, 28×58×117cm</v>
+        <v>LM 5-Tier Multifunctional Shoe Rack, Space-Saving Shoe &amp; Storage Organizer for Entrance Bedroom Dormitory, White</v>
       </c>
       <c r="B50" t="str">
-        <v>KSh 1,399</v>
+        <v>KSh 1,435</v>
       </c>
       <c r="C50" t="str">
-        <v>KSh 2,010</v>
+        <v>KSh 1,742</v>
       </c>
       <c r="D50" t="str">
-        <v>30%</v>
+        <v>18%</v>
       </c>
       <c r="F50" t="str">
-        <v>https://www.jumia.co.ke/lm-6-tier-shoe-organizer-with-translucent-panels-space-saving-shoe-storage-cabinet-for-entrance-home-2858117cm-327990966.html</v>
+        <v>https://www.jumia.co.ke/lm-5-tier-multifunctional-shoe-rack-space-saving-shoe-storage-organizer-for-entrance-bedroom-dormitory-white-327990870.html</v>
       </c>
       <c r="G50" t="str">
-        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/66/9099723/1.jpg?6182</v>
+        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/07/8099723/1.jpg?5913</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>VANHUHU Men's Italian Formal Oxford Loafers Lace up Flat Business Shoes Black</v>
+        <v>cloudoon Coat Rack with 4-Tier Shoe Rack, Double Hooks, Metal Entryway Organizer for Shoes, Bags &amp; Clothes</v>
       </c>
       <c r="B51" t="str">
-        <v>KSh 1,981</v>
+        <v>KSh 1,800</v>
       </c>
       <c r="C51" t="str">
-        <v>KSh 2,412</v>
+        <v>KSh 3,600</v>
       </c>
       <c r="D51" t="str">
-        <v>18%</v>
+        <v>50%</v>
       </c>
       <c r="F51" t="str">
-        <v>https://www.jumia.co.ke/vanhuhu-mens-italian-formal-oxford-loafers-lace-up-flat-business-shoes-black-326347332.html</v>
+        <v>https://www.jumia.co.ke/cloudoon-coat-rack-with-4-tier-shoe-rack-double-hooks-metal-entryway-organizer-for-shoes-bags-clothes-318843368.html</v>
       </c>
       <c r="G51" t="str">
-        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/23/3743623/1.jpg?3272</v>
+        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/86/3348813/1.jpg?6067</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Lindy Dustproof Single Wardrobe, Coffee</v>
+        <v>TIMBUTUS 7-layer Steel Pipe Shoe Rack (56 * 25.5 * 125cm)</v>
       </c>
       <c r="B52" t="str">
-        <v>KSh 1,407</v>
+        <v>KSh 1,648</v>
       </c>
       <c r="C52" t="str">
-        <v>KSh 3,350</v>
+        <v>KSh 2,680</v>
       </c>
       <c r="D52" t="str">
-        <v>58%</v>
+        <v>39%</v>
       </c>
       <c r="F52" t="str">
-        <v>https://www.jumia.co.ke/lindy-dustproof-single-wardrobe-coffee-326421887.html</v>
+        <v>https://www.jumia.co.ke/timbutus-7-layer-steel-pipe-shoe-rack-56-25.5-125cm-319350213.html</v>
       </c>
       <c r="G52" t="str">
-        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/78/8124623/1.jpg?4875</v>
+        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/31/2053913/1.jpg?0328</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>LM Mobile Garment Rack with Hanging Rail &amp; Storage Shelves, Space-Saving Clothes Organizer with Wheels, Black</v>
+        <v>SHJO Loafers Men Comfortable Business Faux Leather Lightweight Slip-on Driving Moccasins Casual Shoes - Black</v>
       </c>
       <c r="B53" t="str">
-        <v>KSh 1,420</v>
+        <v>KSh 648</v>
       </c>
       <c r="C53" t="str">
-        <v>KSh 1,742</v>
+        <v>KSh 1,474</v>
       </c>
       <c r="D53" t="str">
-        <v>19%</v>
+        <v>56%</v>
       </c>
       <c r="F53" t="str">
-        <v>https://www.jumia.co.ke/lm-mobile-garment-rack-with-hanging-rail-storage-shelves-space-saving-clothes-organizer-with-wheels-black-327991017.html</v>
+        <v>https://www.jumia.co.ke/shjo-loafers-men-comfortable-business-faux-leather-lightweight-slip-on-driving-moccasins-casual-shoes-black-326562727.html</v>
       </c>
       <c r="G53" t="str">
-        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/71/0199723/1.jpg?7619</v>
+        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/72/7265623/1.jpg?6811</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Shoe Rack Organizer for Entryway Space-Saving Design for Efficient Shoe Storage and Easy to Clean for Closets and Living Spaces</v>
+        <v>VANHUHU Men's Italian Formal Loafers &amp; Slip-Ons Flat Business Shoes Black</v>
       </c>
       <c r="B54" t="str">
-        <v>KSh 1,399</v>
+        <v>KSh 2,010</v>
       </c>
       <c r="C54" t="str">
-        <v>KSh 3,288</v>
+        <v>KSh 2,412</v>
       </c>
       <c r="D54" t="str">
-        <v>58%</v>
+        <v>17%</v>
       </c>
       <c r="F54" t="str">
-        <v>https://www.jumia.co.ke/generic-shoe-rack-organizer-for-entryway-space-saving-design-for-efficient-shoe-storage-and-easy-to-clean-for-closets-and-living-spaces-326496878.html</v>
+        <v>https://www.jumia.co.ke/vanhuhu-mens-italian-formal-loafers-slip-ons-flat-business-shoes-black-327523048.html</v>
       </c>
       <c r="G54" t="str">
-        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/87/8694623/1.jpg?9672</v>
+        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/84/0325723/1.jpg?4296</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>LM 5-Tier Multifunctional Shoe Rack, Space-Saving Shoe &amp; Storage Organizer for Entrance Bedroom Dormitory, White</v>
+        <v>Men's Black Loafers - Casual Slip-On Business Shoes Rubber Sole</v>
       </c>
       <c r="B55" t="str">
-        <v>KSh 1,435</v>
+        <v>KSh 1,301</v>
       </c>
       <c r="C55" t="str">
-        <v>KSh 1,742</v>
+        <v>KSh 2,412</v>
       </c>
       <c r="D55" t="str">
-        <v>18%</v>
+        <v>46%</v>
       </c>
       <c r="F55" t="str">
-        <v>https://www.jumia.co.ke/lm-5-tier-multifunctional-shoe-rack-space-saving-shoe-storage-organizer-for-entrance-bedroom-dormitory-white-327990870.html</v>
+        <v>https://www.jumia.co.ke/fashion-mens-black-loafers-casual-slip-on-business-shoes-rubber-sole-326458753.html</v>
       </c>
       <c r="G55" t="str">
-        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/07/8099723/1.jpg?5913</v>
+        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/35/7854623/1.jpg?7122</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Lindy Single Row 9 Layer Shoe Wardrobe - Brown</v>
+        <v>Men's Formal Oxford Official Corporate Lace up Flat Business Shoes Black</v>
       </c>
       <c r="B56" t="str">
-        <v>KSh 1,206</v>
+        <v>KSh 1,800</v>
       </c>
       <c r="C56" t="str">
-        <v>KSh 2,680</v>
+        <v>KSh 2,412</v>
       </c>
       <c r="D56" t="str">
-        <v>55%</v>
+        <v>25%</v>
       </c>
       <c r="F56" t="str">
-        <v>https://www.jumia.co.ke/lindy-single-row-9-layer-shoe-wardrobe-brown-325684631.html</v>
+        <v>https://www.jumia.co.ke/fashion-mens-formal-oxford-official-corporate-lace-up-flat-business-shoes-black-326458043.html</v>
       </c>
       <c r="G56" t="str">
-        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/13/6486523/1.jpg?4045</v>
+        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/34/0854623/1.jpg?2761</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Lindy Foldable Closet Cabinet - 10 Shelves - Grey</v>
+        <v>VANHUHU Men's Italian Formal Oxford Loafers Lace up Flat Business Shoes Black</v>
       </c>
       <c r="B57" t="str">
-        <v>KSh 2,010</v>
+        <v>KSh 1,981</v>
       </c>
       <c r="C57" t="str">
-        <v>KSh 2,680</v>
+        <v>KSh 2,412</v>
       </c>
       <c r="D57" t="str">
-        <v>25%</v>
+        <v>18%</v>
       </c>
       <c r="F57" t="str">
-        <v>https://www.jumia.co.ke/foldable-closet-cabinet-10-shelves-grey-lindy-mpg9519558.html</v>
+        <v>https://www.jumia.co.ke/vanhuhu-mens-italian-formal-oxford-loafers-lace-up-flat-business-shoes-black-326347332.html</v>
       </c>
       <c r="G57" t="str">
-        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/30/0182523/1.jpg?5010</v>
+        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/23/3743623/1.jpg?3272</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>TIMBUTUS 7-layer Steel Pipe Shoe Rack (56 * 25.5 * 125cm)</v>
+        <v>Men's  Formal Glossy Tassel Brogue Shoes Loafers &amp; Slip-ons Formal Black</v>
       </c>
       <c r="B58" t="str">
-        <v>KSh 1,648</v>
+        <v>KSh 2,137 - KSh 2,726</v>
       </c>
       <c r="C58" t="str">
-        <v>KSh 2,680</v>
+        <v>KSh 3,087</v>
       </c>
       <c r="D58" t="str">
-        <v>39%</v>
+        <v>31%</v>
       </c>
       <c r="F58" t="str">
-        <v>https://www.jumia.co.ke/timbutus-7-layer-steel-pipe-shoe-rack-56-25.5-125cm-319350213.html</v>
+        <v>https://www.jumia.co.ke/fashion-mens-formal-glossy-tassel-brogue-shoes-loafers-slip-ons-formal-black-178013928.html</v>
       </c>
       <c r="G58" t="str">
-        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/31/2053913/1.jpg?0328</v>
+        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/82/9310871/1.jpg?8535</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>VANHUHU Men's Italian Formal Loafers &amp; Slip-Ons Flat Business Shoes Black</v>
+        <v>SHJO Dress Shoes Men Business Office Wedding Faux Leather Non-slip Wear-resistant Comfortable Slip On Formal Loafers Black</v>
       </c>
       <c r="B59" t="str">
-        <v>KSh 2,010</v>
+        <v>KSh 1,024 - KSh 1,359</v>
       </c>
       <c r="C59" t="str">
-        <v>KSh 2,412</v>
+        <v>KSh 3,082</v>
       </c>
       <c r="D59" t="str">
-        <v>17%</v>
+        <v>67%</v>
       </c>
       <c r="F59" t="str">
-        <v>https://www.jumia.co.ke/vanhuhu-mens-italian-formal-loafers-slip-ons-flat-business-shoes-black-327523048.html</v>
+        <v>https://www.jumia.co.ke/shjo-dress-shoes-men-business-office-wedding-faux-leather-non-slip-wear-resistant-comfortable-slip-on-formal-loafers-black-326506490.html</v>
       </c>
       <c r="G59" t="str">
-        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/84/0325723/1.jpg?4296</v>
+        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/09/4605623/1.jpg?0336</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>SHJO Loafers Men Comfortable Business Faux Leather Lightweight Slip-on Driving Moccasins Casual Shoes - Black</v>
+        <v>Lindy Dustproof Single Wardrobe, Coffee</v>
       </c>
       <c r="B60" t="str">
-        <v>KSh 648</v>
+        <v>KSh 1,407</v>
       </c>
       <c r="C60" t="str">
-        <v>KSh 1,474</v>
+        <v>KSh 3,350</v>
       </c>
       <c r="D60" t="str">
-        <v>56%</v>
+        <v>58%</v>
       </c>
       <c r="F60" t="str">
-        <v>https://www.jumia.co.ke/shjo-loafers-men-comfortable-business-faux-leather-lightweight-slip-on-driving-moccasins-casual-shoes-black-326562727.html</v>
+        <v>https://www.jumia.co.ke/lindy-dustproof-single-wardrobe-coffee-326421887.html</v>
       </c>
       <c r="G60" t="str">
-        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/72/7265623/1.jpg?6811</v>
+        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/78/8124623/1.jpg?4875</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Banagat Men's Black PU Leather Slip-On Formal Loafers</v>
+        <v>Lindy Single Row 9 Layer Shoe Wardrobe, Grey</v>
       </c>
       <c r="B61" t="str">
-        <v>KSh 2,950</v>
+        <v>KSh 1,541</v>
       </c>
       <c r="C61" t="str">
-        <v>KSh 6,030</v>
+        <v>KSh 2,680</v>
       </c>
       <c r="D61" t="str">
-        <v>51%</v>
+        <v>43%</v>
       </c>
       <c r="F61" t="str">
-        <v>https://www.jumia.co.ke/banagat-mens-black-pu-leather-slip-on-formal-loafers-325681473.html</v>
+        <v>https://www.jumia.co.ke/lindy-single-row-9-layer-shoe-wardrobe-grey-300560306.html</v>
       </c>
       <c r="G61" t="str">
-        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/37/4186523/1.jpg?4332</v>
+        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/60/3065003/1.jpg?9487</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Men's Black Business Leather Slip-On Formal Shoes</v>
+        <v>TIMBUTUS Dustproof Shoe Rack Organizer – 7-layer Storage Cabinet with Cover  (60 * 30 * 123cm)</v>
       </c>
       <c r="B62" t="str">
-        <v>KSh 1,587</v>
+        <v>KSh 1,474</v>
       </c>
       <c r="C62" t="str">
-        <v>KSh 3,087</v>
+        <v>KSh 2,680</v>
       </c>
       <c r="D62" t="str">
-        <v>49%</v>
+        <v>45%</v>
       </c>
       <c r="F62" t="str">
-        <v>https://www.jumia.co.ke/fashion-mens-black-business-leather-slip-on-formal-shoes-314491006.html</v>
+        <v>https://www.jumia.co.ke/timbutus-dustproof-shoe-rack-organizer-7-layer-storage-cabinet-with-cover-60-30-123cm-325317704.html</v>
       </c>
       <c r="G62" t="str">
-        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/60/0194413/1.jpg?8308</v>
+        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/40/7713523/1.jpg?3816</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Men's Black Loafers - Casual Slip-On Business Shoes Rubber Sole</v>
+        <v>5-Tier Freestanding Coat Rack &amp; Shoe Organizer - White</v>
       </c>
       <c r="B63" t="str">
-        <v>KSh 1,301</v>
+        <v>KSh 1,150</v>
       </c>
       <c r="C63" t="str">
-        <v>KSh 2,412</v>
+        <v>KSh 2,010</v>
       </c>
       <c r="D63" t="str">
-        <v>46%</v>
+        <v>43%</v>
       </c>
       <c r="F63" t="str">
-        <v>https://www.jumia.co.ke/fashion-mens-black-loafers-casual-slip-on-business-shoes-rubber-sole-326458753.html</v>
+        <v>https://www.jumia.co.ke/generic-5-tier-freestanding-coat-rack-shoe-organizer-white-327436845.html</v>
       </c>
       <c r="G63" t="str">
-        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/35/7854623/1.jpg?7122</v>
+        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/54/8634723/1.jpg?8298</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Men's  Formal Glossy Tassel Brogue Shoes Loafers &amp; Slip-ons Formal Black</v>
+        <v>Banagat Men's Black PU Leather Casual Oxfords Shoes</v>
       </c>
       <c r="B64" t="str">
-        <v>KSh 2,137 - KSh 2,726</v>
+        <v>KSh 1,770 - KSh 2,258</v>
       </c>
       <c r="C64" t="str">
-        <v>KSh 3,087</v>
+        <v>KSh 2,680</v>
       </c>
       <c r="D64" t="str">
-        <v>31%</v>
+        <v>34%</v>
       </c>
       <c r="F64" t="str">
-        <v>https://www.jumia.co.ke/fashion-mens-formal-glossy-tassel-brogue-shoes-loafers-slip-ons-formal-black-178013928.html</v>
+        <v>https://www.jumia.co.ke/banagat-mens-black-pu-leather-casual-oxfords-shoes-317205452.html</v>
       </c>
       <c r="G64" t="str">
-        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/82/9310871/1.jpg?8535</v>
+        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/25/4502713/1.jpg?0309</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Men's Formal Oxford Official Corporate Lace up Flat Business Shoes Black</v>
+        <v>Men's Formal Flat Business Shoes Loafers Italian Official Black</v>
       </c>
       <c r="B65" t="str">
-        <v>KSh 1,800</v>
+        <v>KSh 1,601</v>
       </c>
       <c r="C65" t="str">
         <v>KSh 2,412</v>
       </c>
       <c r="D65" t="str">
-        <v>25%</v>
+        <v>34%</v>
       </c>
       <c r="F65" t="str">
-        <v>https://www.jumia.co.ke/fashion-mens-formal-oxford-official-corporate-lace-up-flat-business-shoes-black-326458043.html</v>
+        <v>https://www.jumia.co.ke/fashion-mens-formal-flat-business-shoes-loafers-italian-official-black-326480486.html</v>
       </c>
       <c r="G65" t="str">
-        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/34/0854623/1.jpg?2761</v>
+        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/68/4084623/1.jpg?6647</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Lindy Single Row 9 Layer Shoe Wardrobe, Grey</v>
+        <v>VANHUHU Men's Italian Formal Loafers &amp; Slip-Ons Flat Business Shoes Black</v>
       </c>
       <c r="B66" t="str">
-        <v>KSh 1,541</v>
+        <v>KSh 1,742</v>
       </c>
       <c r="C66" t="str">
-        <v>KSh 2,680</v>
+        <v>KSh 2,010</v>
       </c>
       <c r="D66" t="str">
-        <v>43%</v>
+        <v>13%</v>
       </c>
       <c r="F66" t="str">
-        <v>https://www.jumia.co.ke/lindy-single-row-9-layer-shoe-wardrobe-grey-300560306.html</v>
+        <v>https://www.jumia.co.ke/vanhuhu-mens-italian-formal-loafers-slip-ons-flat-business-shoes-black-327797228.html</v>
       </c>
       <c r="G66" t="str">
-        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/60/3065003/1.jpg?9487</v>
+        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/82/2797723/1.jpg?2853</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>TIMBUTUS Dustproof Shoe Rack Organizer – 7-layer Storage Cabinet with Cover  (60 * 30 * 123cm)</v>
+        <v>Men's Formal Shoes Black Leather Quality  Shoe  British Business  Slip-On  Wedding Shoes</v>
       </c>
       <c r="B67" t="str">
-        <v>KSh 1,474</v>
+        <v>KSh 1,274</v>
       </c>
       <c r="C67" t="str">
-        <v>KSh 2,680</v>
+        <v>KSh 3,216</v>
       </c>
       <c r="D67" t="str">
-        <v>45%</v>
+        <v>60%</v>
       </c>
       <c r="F67" t="str">
-        <v>https://www.jumia.co.ke/timbutus-dustproof-shoe-rack-organizer-7-layer-storage-cabinet-with-cover-60-30-123cm-325317704.html</v>
+        <v>https://www.jumia.co.ke/fashion-mens-formal-shoes-black-leather-quality-shoe-british-business-slip-on-wedding-shoes-326496929.html</v>
       </c>
       <c r="G67" t="str">
-        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/40/7713523/1.jpg?3816</v>
+        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/92/9694623/1.jpg?0513</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Yxahee 6-Tier  Multifunctional Freestanding Shoe Rack Collapsible Shoe Rack</v>
+        <v>SHJO Sneakers Men Casual Synthetic Leather Breathable Lightweight Flat Walking Fashion Trendy Shoes - White</v>
       </c>
       <c r="B68" t="str">
-        <v>KSh 1,072</v>
+        <v>KSh 959 - KSh 1,020</v>
       </c>
       <c r="C68" t="str">
-        <v>KSh 2,204</v>
+        <v>KSh 2,010</v>
       </c>
       <c r="D68" t="str">
-        <v>51%</v>
+        <v>52%</v>
       </c>
       <c r="F68" t="str">
-        <v>https://www.jumia.co.ke/yxahee-6-tier-multifunctional-freestanding-shoe-rack-collapsible-shoe-rack-167092129.html</v>
+        <v>https://www.jumia.co.ke/shjo-sneakers-men-casual-synthetic-leather-breathable-lightweight-flat-walking-fashion-trendy-shoes-white-326506519.html</v>
       </c>
       <c r="G68" t="str">
-        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/92/1290761/1.jpg?6783</v>
+        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/91/5605623/1.jpg?5421</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>5-Tier Freestanding Coat Rack &amp; Shoe Organizer - White</v>
+        <v>SHJO Men'S Stylish Black Slip-On Dress Shoes - Business Casual Wedding Party</v>
       </c>
       <c r="B69" t="str">
-        <v>KSh 1,150</v>
+        <v>KSh 1,147</v>
       </c>
       <c r="C69" t="str">
-        <v>KSh 2,010</v>
+        <v>KSh 2,278</v>
       </c>
       <c r="D69" t="str">
-        <v>43%</v>
+        <v>50%</v>
       </c>
       <c r="F69" t="str">
-        <v>https://www.jumia.co.ke/generic-5-tier-freestanding-coat-rack-shoe-organizer-white-327436845.html</v>
+        <v>https://www.jumia.co.ke/shjo-mens-stylish-black-slip-on-dress-shoes-business-casual-wedding-party-326849895.html</v>
       </c>
       <c r="G69" t="str">
-        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/54/8634723/1.jpg?8298</v>
+        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/59/8948623/1.jpg?7873</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Banagat Men's Black PU Leather Casual Oxfords Shoes</v>
+        <v>VANHUHU Men's Italian Formal Loafers Lace up Flat Business Shoes Gold</v>
       </c>
       <c r="B70" t="str">
-        <v>KSh 1,770 - KSh 2,258</v>
+        <v>KSh 2,350</v>
       </c>
       <c r="C70" t="str">
         <v>KSh 2,680</v>
       </c>
       <c r="D70" t="str">
-        <v>34%</v>
+        <v>12%</v>
       </c>
       <c r="F70" t="str">
-        <v>https://www.jumia.co.ke/banagat-mens-black-pu-leather-casual-oxfords-shoes-317205452.html</v>
+        <v>https://www.jumia.co.ke/vanhuhu-mens-italian-formal-loafers-lace-up-flat-business-shoes-gold-327518056.html</v>
       </c>
       <c r="G70" t="str">
-        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/25/4502713/1.jpg?0309</v>
+        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/65/0815723/1.jpg?5057</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Men's Formal Flat Business Shoes Loafers Italian Official Black</v>
+        <v>Banagat Men's Comfortable Casual Loafers &amp; Slip-ons Formal Corporate Shoes Brown</v>
       </c>
       <c r="B71" t="str">
-        <v>KSh 1,601</v>
+        <v>KSh 2,900</v>
       </c>
       <c r="C71" t="str">
-        <v>KSh 2,412</v>
+        <v>KSh 4,690</v>
       </c>
       <c r="D71" t="str">
-        <v>34%</v>
+        <v>38%</v>
       </c>
       <c r="F71" t="str">
-        <v>https://www.jumia.co.ke/fashion-mens-formal-flat-business-shoes-loafers-italian-official-black-326480486.html</v>
+        <v>https://www.jumia.co.ke/banagat-mens-comfortable-casual-loafers-slip-ons-formal-corporate-shoes-brown-325719701.html</v>
       </c>
       <c r="G71" t="str">
-        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/68/4084623/1.jpg?6647</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="str">
-        <v>VANHUHU Men's Italian Formal Loafers Lace up Flat Business Shoes Gold</v>
-      </c>
-      <c r="B72" t="str">
-        <v>KSh 2,350</v>
-      </c>
-      <c r="C72" t="str">
-        <v>KSh 2,680</v>
-      </c>
-      <c r="D72" t="str">
-        <v>12%</v>
-      </c>
-      <c r="F72" t="str">
-        <v>https://www.jumia.co.ke/vanhuhu-mens-italian-formal-loafers-lace-up-flat-business-shoes-gold-327518056.html</v>
-      </c>
-      <c r="G72" t="str">
-        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/65/0815723/1.jpg?5057</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="str">
-        <v>VANHUHU Men's Italian Formal Loafers &amp; Slip-Ons Flat Business Shoes Black</v>
-      </c>
-      <c r="B73" t="str">
-        <v>KSh 1,742</v>
-      </c>
-      <c r="C73" t="str">
-        <v>KSh 2,010</v>
-      </c>
-      <c r="D73" t="str">
-        <v>13%</v>
-      </c>
-      <c r="F73" t="str">
-        <v>https://www.jumia.co.ke/vanhuhu-mens-italian-formal-loafers-slip-ons-flat-business-shoes-black-327797228.html</v>
-      </c>
-      <c r="G73" t="str">
-        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/82/2797723/1.jpg?2853</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="str">
-        <v>VEOUNDK Men's Low-Top Martin Boots - Black</v>
-      </c>
-      <c r="B74" t="str">
-        <v>KSh 986</v>
-      </c>
-      <c r="C74" t="str">
-        <v>KSh 2,025</v>
-      </c>
-      <c r="D74" t="str">
-        <v>51%</v>
-      </c>
-      <c r="F74" t="str">
-        <v>https://www.jumia.co.ke/veoundk-mens-low-top-martin-boots-black-327482316.html</v>
-      </c>
-      <c r="G74" t="str">
-        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/61/3284723/1.jpg?4665</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="str">
-        <v>VEOUNDK New Men's Fashion Leather Shoes - black</v>
-      </c>
-      <c r="B75" t="str">
-        <v>KSh 1,327</v>
-      </c>
-      <c r="C75" t="str">
-        <v>KSh 2,144</v>
-      </c>
-      <c r="D75" t="str">
-        <v>38%</v>
-      </c>
-      <c r="F75" t="str">
-        <v>https://www.jumia.co.ke/veoundk-new-mens-fashion-leather-shoes-black-327524812.html</v>
-      </c>
-      <c r="G75" t="str">
-        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/21/8425723/1.jpg?6103</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="str">
-        <v>GALUIN Men's Flat Designer Footwear Breathable Casual Loafers Italian Shoes Black</v>
-      </c>
-      <c r="B76" t="str">
-        <v>KSh 780</v>
-      </c>
-      <c r="C76" t="str">
-        <v>KSh 1,674</v>
-      </c>
-      <c r="D76" t="str">
-        <v>53%</v>
-      </c>
-      <c r="F76" t="str">
-        <v>https://www.jumia.co.ke/galuin-mens-flat-designer-footwear-breathable-casual-loafers-italian-shoes-black-305033384.html</v>
-      </c>
-      <c r="G76" t="str">
-        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/48/3330503/1.jpg?4848</v>
+        <v>https://ke.jumia.is/unsafe/fit-in/300x300/filters:fill(white)/product/10/7917523/1.jpg?4341</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G76"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G71"/>
   </ignoredErrors>
 </worksheet>
 </file>